--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487212_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487212_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.1648</v>
+        <v>5.3582</v>
       </c>
       <c r="E2" t="n">
-        <v>4.144</v>
+        <v>4.2035</v>
       </c>
       <c r="F2" t="n">
-        <v>1.0208</v>
+        <v>1.1547</v>
       </c>
       <c r="G2" t="n">
         <v>3.5342</v>
@@ -610,13 +610,13 @@
         <v>1.7371</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8163</v>
+        <v>1.0097</v>
       </c>
       <c r="T2" t="n">
-        <v>0.8884</v>
+        <v>0.9479</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0721</v>
+        <v>0.0618</v>
       </c>
       <c r="V2" t="n">
         <v>0.0422</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.4999</v>
+        <v>4.9411</v>
       </c>
       <c r="E3" t="n">
-        <v>2.8459</v>
+        <v>3.0462</v>
       </c>
       <c r="F3" t="n">
-        <v>1.654</v>
+        <v>1.8949</v>
       </c>
       <c r="G3" t="n">
         <v>2.5543</v>
@@ -688,13 +688,13 @@
         <v>1.5441</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1157</v>
+        <v>0.5569</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1468</v>
+        <v>0.347</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0311</v>
+        <v>0.2098</v>
       </c>
       <c r="V3" t="n">
         <v>0.2859</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. VASQUEZ BAUTISTA</t>
+          <t>M. CARRETERO GARCÍA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.0399</v>
+        <v>3.6403</v>
       </c>
       <c r="E4" t="n">
-        <v>3.3381</v>
+        <v>1.4264</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7018</v>
+        <v>2.2139</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.3147</v>
+        <v>2.5639</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.6552</v>
+        <v>0.7845</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3406</v>
+        <v>1.7793</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.5881</v>
+        <v>2.4159</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.3614</v>
+        <v>0.4709</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7733</v>
+        <v>1.945</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.7266</v>
+        <v>0.148</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.2939</v>
+        <v>0.3137</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.4327</v>
+        <v>-0.1657</v>
       </c>
       <c r="P4" t="n">
-        <v>0.386</v>
+        <v>-0.193</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.965</v>
+        <v>-1.9301</v>
       </c>
       <c r="R4" t="n">
-        <v>1.3511</v>
+        <v>1.7371</v>
       </c>
       <c r="S4" t="n">
-        <v>4.3123</v>
+        <v>1.2694</v>
       </c>
       <c r="T4" t="n">
-        <v>3.6632</v>
+        <v>0.9406</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6491</v>
+        <v>0.3288</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6562</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.228</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.5717</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. CARRETERO GARCÍA</t>
+          <t>D. CARRETERO GARCIA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.3062</v>
+        <v>2.9756</v>
       </c>
       <c r="E5" t="n">
-        <v>1.2261</v>
+        <v>1.62</v>
       </c>
       <c r="F5" t="n">
-        <v>2.08</v>
+        <v>1.3556</v>
       </c>
       <c r="G5" t="n">
-        <v>2.5639</v>
+        <v>1.7014</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7845</v>
+        <v>1.4915</v>
       </c>
       <c r="I5" t="n">
-        <v>1.7793</v>
+        <v>0.2099</v>
       </c>
       <c r="J5" t="n">
-        <v>2.4159</v>
+        <v>2.1744</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4709</v>
+        <v>0.8641</v>
       </c>
       <c r="L5" t="n">
-        <v>1.945</v>
+        <v>1.3102</v>
       </c>
       <c r="M5" t="n">
-        <v>0.148</v>
+        <v>-0.473</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3137</v>
+        <v>0.6273</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.1657</v>
+        <v>-1.1003</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.193</v>
+        <v>0.579</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.9301</v>
+        <v>-0.965</v>
       </c>
       <c r="R5" t="n">
-        <v>1.7371</v>
+        <v>1.5441</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9353</v>
+        <v>1.3514</v>
       </c>
       <c r="T5" t="n">
-        <v>0.7403</v>
+        <v>1.0669</v>
       </c>
       <c r="U5" t="n">
-        <v>0.195</v>
+        <v>0.2845</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-0.6562</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>-0.6562</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. CARRETERO GARCIA</t>
+          <t>J. HORCAJO GARCÍA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.0499</v>
+        <v>1.9204</v>
       </c>
       <c r="E6" t="n">
-        <v>1.5605</v>
+        <v>1.2086</v>
       </c>
       <c r="F6" t="n">
-        <v>1.4895</v>
+        <v>0.7118</v>
       </c>
       <c r="G6" t="n">
-        <v>1.7014</v>
+        <v>0.5393</v>
       </c>
       <c r="H6" t="n">
-        <v>1.4915</v>
+        <v>0.1501</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2099</v>
+        <v>0.3891</v>
       </c>
       <c r="J6" t="n">
-        <v>2.1744</v>
+        <v>0.779</v>
       </c>
       <c r="K6" t="n">
-        <v>0.8641</v>
+        <v>0.1035</v>
       </c>
       <c r="L6" t="n">
-        <v>1.3102</v>
+        <v>0.6755</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.473</v>
+        <v>-0.2397</v>
       </c>
       <c r="N6" t="n">
-        <v>0.6273</v>
+        <v>0.0466</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.1003</v>
+        <v>-0.2863</v>
       </c>
       <c r="P6" t="n">
-        <v>0.579</v>
+        <v>0.965</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.965</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5441</v>
+        <v>0.965</v>
       </c>
       <c r="S6" t="n">
-        <v>1.4257</v>
+        <v>0.4161</v>
       </c>
       <c r="T6" t="n">
-        <v>1.0074</v>
+        <v>0.4297</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4184</v>
+        <v>-0.0136</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.6562</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.6562</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. HORCAJO GARCÍA</t>
+          <t>A. VASQUEZ BAUTISTA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.7271</v>
+        <v>1.8834</v>
       </c>
       <c r="E7" t="n">
-        <v>1.1491</v>
+        <v>1.2351</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5779</v>
+        <v>0.6483</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5393</v>
+        <v>-1.3147</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1501</v>
+        <v>-1.6552</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3891</v>
+        <v>0.3406</v>
       </c>
       <c r="J7" t="n">
-        <v>0.779</v>
+        <v>-0.5881</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1035</v>
+        <v>-1.3614</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6755</v>
+        <v>0.7733</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.2397</v>
+        <v>-0.7266</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0466</v>
+        <v>-0.2939</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.2863</v>
+        <v>-0.4327</v>
       </c>
       <c r="P7" t="n">
-        <v>0.965</v>
+        <v>0.386</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.965</v>
       </c>
       <c r="R7" t="n">
-        <v>0.965</v>
+        <v>1.3511</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2228</v>
+        <v>2.1558</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3702</v>
+        <v>1.5603</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1474</v>
+        <v>0.5955</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.6562</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.228</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.5717</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. FERNANDEZ CRESPO</t>
+          <t>C. HERNÁNDEZ MARTÍN</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.2326</v>
+        <v>1.068</v>
       </c>
       <c r="E8" t="n">
-        <v>0.003</v>
+        <v>0.7409</v>
       </c>
       <c r="F8" t="n">
-        <v>1.2296</v>
+        <v>0.3271</v>
       </c>
       <c r="G8" t="n">
-        <v>1.4626</v>
+        <v>-0.8813</v>
       </c>
       <c r="H8" t="n">
-        <v>1.4676</v>
+        <v>2.3454</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.005</v>
+        <v>-3.2267</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9548</v>
+        <v>0.3386</v>
       </c>
       <c r="K8" t="n">
-        <v>0.9469</v>
+        <v>1.511</v>
       </c>
       <c r="L8" t="n">
-        <v>0.007900000000000001</v>
+        <v>-1.1724</v>
       </c>
       <c r="M8" t="n">
-        <v>0.5078</v>
+        <v>-1.2199</v>
       </c>
       <c r="N8" t="n">
-        <v>0.5207000000000001</v>
+        <v>0.8343</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.0129</v>
+        <v>-2.0542</v>
       </c>
       <c r="P8" t="n">
+        <v>-0.193</v>
+      </c>
+      <c r="Q8" t="n">
         <v>-0.965</v>
       </c>
-      <c r="Q8" t="n">
-        <v>-1.9301</v>
-      </c>
       <c r="R8" t="n">
-        <v>0.965</v>
+        <v>0.772</v>
       </c>
       <c r="S8" t="n">
-        <v>1.3068</v>
+        <v>2.1423</v>
       </c>
       <c r="T8" t="n">
-        <v>0.9782999999999999</v>
+        <v>1.3673</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3285</v>
+        <v>0.775</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.5717</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.5717</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>C. HERNÁNDEZ MARTÍN</t>
+          <t>A. FERNANDEZ CRESPO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3025</v>
+        <v>0.6575</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.4797</v>
+        <v>-0.4382</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7822</v>
+        <v>1.0957</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.8813</v>
+        <v>1.4626</v>
       </c>
       <c r="H9" t="n">
-        <v>2.3454</v>
+        <v>1.4676</v>
       </c>
       <c r="I9" t="n">
-        <v>-3.2267</v>
+        <v>-0.005</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3386</v>
+        <v>0.9548</v>
       </c>
       <c r="K9" t="n">
-        <v>1.511</v>
+        <v>0.9469</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.1724</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.2199</v>
+        <v>0.5078</v>
       </c>
       <c r="N9" t="n">
-        <v>0.8343</v>
+        <v>0.5207000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>-2.0542</v>
+        <v>-0.0129</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.193</v>
+        <v>-0.965</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.965</v>
+        <v>-1.9301</v>
       </c>
       <c r="R9" t="n">
-        <v>0.772</v>
+        <v>0.965</v>
       </c>
       <c r="S9" t="n">
-        <v>1.3768</v>
+        <v>0.7317</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1468</v>
+        <v>0.5371</v>
       </c>
       <c r="U9" t="n">
-        <v>1.2301</v>
+        <v>0.1946</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-0.5717</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.5717</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. TOURE</t>
+          <t>J. TEJERINA TEJEDO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.1211</v>
+        <v>0.1968</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.6449</v>
+        <v>-0.1016</v>
       </c>
       <c r="F10" t="n">
-        <v>1.5238</v>
+        <v>0.2985</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.0697</v>
+        <v>0.0813</v>
       </c>
       <c r="H10" t="n">
-        <v>0.182</v>
+        <v>0.5455</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.2517</v>
+        <v>-0.4641</v>
       </c>
       <c r="J10" t="n">
-        <v>0.391</v>
+        <v>1.1549</v>
       </c>
       <c r="K10" t="n">
-        <v>0.2689</v>
+        <v>0.5122</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1221</v>
+        <v>0.6425999999999999</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.4607</v>
+        <v>-1.0735</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.08690000000000001</v>
+        <v>0.0332</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.3738</v>
+        <v>-1.1067</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.5441</v>
+        <v>-0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.8951</v>
+        <v>-1.9301</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3511</v>
+        <v>1.9301</v>
       </c>
       <c r="S10" t="n">
-        <v>1.5084</v>
+        <v>1.3435</v>
       </c>
       <c r="T10" t="n">
-        <v>0.8593</v>
+        <v>0.6736</v>
       </c>
       <c r="U10" t="n">
-        <v>0.6491</v>
+        <v>0.6699000000000001</v>
       </c>
       <c r="V10" t="n">
-        <v>0.9843</v>
+        <v>-1.228</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0.9843</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>V. TAVERAS RAFAEL</t>
+          <t>A. RUIZ FERNÁNDEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.4353</v>
+        <v>-0.1126</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.3893</v>
+        <v>-0.8603</v>
       </c>
       <c r="F11" t="n">
-        <v>0.954</v>
+        <v>0.7476</v>
       </c>
       <c r="G11" t="n">
-        <v>2.0082</v>
+        <v>0.9076</v>
       </c>
       <c r="H11" t="n">
-        <v>2.6722</v>
+        <v>0.2857</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.664</v>
+        <v>0.6219</v>
       </c>
       <c r="J11" t="n">
-        <v>2.1342</v>
+        <v>1.0074</v>
       </c>
       <c r="K11" t="n">
-        <v>1.9714</v>
+        <v>0.3726</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1628</v>
+        <v>0.6348</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.126</v>
+        <v>-0.0998</v>
       </c>
       <c r="N11" t="n">
-        <v>0.7008</v>
+        <v>-0.08690000000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.8268</v>
+        <v>-0.0129</v>
       </c>
       <c r="P11" t="n">
-        <v>-3.0881</v>
+        <v>-1.158</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.8602</v>
+        <v>-1.9301</v>
       </c>
       <c r="R11" t="n">
         <v>0.772</v>
       </c>
       <c r="S11" t="n">
-        <v>1.3008</v>
+        <v>0.1378</v>
       </c>
       <c r="T11" t="n">
-        <v>0.9928</v>
+        <v>0.0625</v>
       </c>
       <c r="U11" t="n">
-        <v>0.308</v>
+        <v>0.07530000000000001</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.6562</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.6562</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. RUIZ FERNÁNDEZ</t>
+          <t>A. TOURE</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.5796</v>
+        <v>-0.2153</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.2202</v>
+        <v>-1.6855</v>
       </c>
       <c r="F12" t="n">
-        <v>0.6405</v>
+        <v>1.4703</v>
       </c>
       <c r="G12" t="n">
-        <v>0.9076</v>
+        <v>-1.0697</v>
       </c>
       <c r="H12" t="n">
-        <v>0.2857</v>
+        <v>0.182</v>
       </c>
       <c r="I12" t="n">
-        <v>0.6219</v>
+        <v>-1.2517</v>
       </c>
       <c r="J12" t="n">
-        <v>1.0074</v>
+        <v>0.391</v>
       </c>
       <c r="K12" t="n">
-        <v>0.3726</v>
+        <v>0.2689</v>
       </c>
       <c r="L12" t="n">
-        <v>0.6348</v>
+        <v>0.1221</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.0998</v>
+        <v>-1.4607</v>
       </c>
       <c r="N12" t="n">
         <v>-0.08690000000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.0129</v>
+        <v>-1.3738</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.158</v>
+        <v>-1.5441</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.9301</v>
+        <v>-2.8951</v>
       </c>
       <c r="R12" t="n">
-        <v>0.772</v>
+        <v>1.3511</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3292</v>
+        <v>1.4142</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2974</v>
+        <v>0.8187</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0317</v>
+        <v>0.5955</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.9843</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>0.9843</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J. TEJERINA TEJEDO</t>
+          <t>V. TAVERAS RAFAEL</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.9979</v>
+        <v>-0.5295</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.1625</v>
+        <v>-1.43</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1646</v>
+        <v>0.9005</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0813</v>
+        <v>2.0082</v>
       </c>
       <c r="H13" t="n">
-        <v>0.5455</v>
+        <v>2.6722</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.4641</v>
+        <v>-0.664</v>
       </c>
       <c r="J13" t="n">
-        <v>1.1549</v>
+        <v>2.1342</v>
       </c>
       <c r="K13" t="n">
-        <v>0.5122</v>
+        <v>1.9714</v>
       </c>
       <c r="L13" t="n">
-        <v>0.6425999999999999</v>
+        <v>0.1628</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.0735</v>
+        <v>-0.126</v>
       </c>
       <c r="N13" t="n">
-        <v>0.0332</v>
+        <v>0.7008</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.1067</v>
+        <v>-0.8268</v>
       </c>
       <c r="P13" t="n">
-        <v>-0</v>
+        <v>-3.0881</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.9301</v>
+        <v>-3.8602</v>
       </c>
       <c r="R13" t="n">
-        <v>1.9301</v>
+        <v>0.772</v>
       </c>
       <c r="S13" t="n">
-        <v>0.1487</v>
+        <v>1.2066</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.3873</v>
+        <v>0.9522</v>
       </c>
       <c r="U13" t="n">
-        <v>0.536</v>
+        <v>0.2545</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.228</v>
+        <v>-0.6562</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>-0.6562</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.228</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>21.189</v>
+        <v>21.7839</v>
       </c>
       <c r="E14" t="n">
-        <v>8.370099999999999</v>
+        <v>8.9651</v>
       </c>
       <c r="F14" t="n">
-        <v>12.8187</v>
+        <v>12.8189</v>
       </c>
       <c r="G14" t="n">
         <v>12.0871</v>
@@ -1522,7 +1522,7 @@
         <v>16.7821</v>
       </c>
       <c r="K14" t="n">
-        <v>9.1166</v>
+        <v>9.116600000000002</v>
       </c>
       <c r="L14" t="n">
         <v>7.6652</v>
@@ -1531,7 +1531,7 @@
         <v>-4.6948</v>
       </c>
       <c r="N14" t="n">
-        <v>4.3376</v>
+        <v>4.337599999999999</v>
       </c>
       <c r="O14" t="n">
         <v>-9.032399999999999</v>
@@ -1546,13 +1546,13 @@
         <v>15.4407</v>
       </c>
       <c r="S14" t="n">
-        <v>13.1404</v>
+        <v>13.7354</v>
       </c>
       <c r="T14" t="n">
-        <v>9.1088</v>
+        <v>9.703799999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>4.0319</v>
+        <v>4.0316</v>
       </c>
       <c r="V14" t="n">
         <v>-1.1435</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.9196</v>
+        <v>3.5674</v>
       </c>
       <c r="E15" t="n">
-        <v>2.7697</v>
+        <v>3.0701</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1499</v>
+        <v>0.4973</v>
       </c>
       <c r="G15" t="n">
         <v>2.0627</v>
@@ -1624,13 +1624,13 @@
         <v>2.7021</v>
       </c>
       <c r="S15" t="n">
-        <v>-2.4556</v>
+        <v>-1.8078</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.9530999999999999</v>
+        <v>-0.6526999999999999</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.5025</v>
+        <v>-1.1551</v>
       </c>
       <c r="V15" t="n">
         <v>2.5404</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7521</v>
+        <v>1.0063</v>
       </c>
       <c r="E16" t="n">
-        <v>1.6147</v>
+        <v>1.4145</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.8626</v>
+        <v>-0.4082</v>
       </c>
       <c r="G16" t="n">
         <v>-0.4848</v>
@@ -1702,13 +1702,13 @@
         <v>3.0881</v>
       </c>
       <c r="S16" t="n">
-        <v>-2.4</v>
+        <v>-2.1459</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.271</v>
+        <v>-0.4712</v>
       </c>
       <c r="U16" t="n">
-        <v>-2.1291</v>
+        <v>-1.6746</v>
       </c>
       <c r="V16" t="n">
         <v>1.5138</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.4302</v>
+        <v>-0.3767</v>
       </c>
       <c r="E17" t="n">
         <v>-0.119</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.3112</v>
+        <v>-0.2577</v>
       </c>
       <c r="G17" t="n">
         <v>-0.3469</v>
@@ -1780,13 +1780,13 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0833</v>
+        <v>-0.0297</v>
       </c>
       <c r="T17" t="n">
         <v>-0.119</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0357</v>
+        <v>0.0892</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.9671</v>
+        <v>-1.4542</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.7485</v>
+        <v>-2.4495</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7814</v>
+        <v>0.9953</v>
       </c>
       <c r="G18" t="n">
         <v>-2.4298</v>
@@ -1858,13 +1858,13 @@
         <v>2.3161</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1117</v>
+        <v>-0.3754</v>
       </c>
       <c r="T18" t="n">
-        <v>0.472</v>
+        <v>-0.229</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3603</v>
+        <v>-0.1464</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.8909</v>
+        <v>-1.851</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.2593</v>
+        <v>-1.4596</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.6316000000000001</v>
+        <v>-0.3913</v>
       </c>
       <c r="G19" t="n">
         <v>-0.9226</v>
@@ -1936,13 +1936,13 @@
         <v>2.1231</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.1614</v>
+        <v>-1.1214</v>
       </c>
       <c r="T19" t="n">
-        <v>0.0119</v>
+        <v>-0.1883</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.1733</v>
+        <v>-0.9330000000000001</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>G. AZANZA TERUEL</t>
+          <t>K. ABU SHAMS SANCHEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.3654</v>
+        <v>-2.1187</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.1063</v>
+        <v>-0.4942</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.2591</v>
+        <v>-1.6245</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.4328</v>
+        <v>-0.1503</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.5195</v>
+        <v>0.825</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.9132</v>
+        <v>-0.9752999999999999</v>
       </c>
       <c r="J20" t="n">
-        <v>0.08210000000000001</v>
+        <v>2.125</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0414</v>
+        <v>1.9871</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0407</v>
+        <v>0.1378</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.5149</v>
+        <v>-2.2753</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.5609</v>
+        <v>-1.1621</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.9539</v>
+        <v>-1.1132</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.193</v>
+        <v>0.386</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.965</v>
+        <v>-1.9301</v>
       </c>
       <c r="R20" t="n">
-        <v>0.772</v>
+        <v>2.3161</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7396</v>
+        <v>-2.0263</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2234</v>
+        <v>-0.9749</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.5162</v>
+        <v>-1.0513</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-0.3281</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.2859</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.614</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>K. ABU SHAMS SANCHEZ</t>
+          <t>G. AZANZA TERUEL</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.3722</v>
+        <v>-2.1384</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.6945</v>
+        <v>-0.9061</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.6777</v>
+        <v>-1.2323</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.1503</v>
+        <v>-1.4328</v>
       </c>
       <c r="H21" t="n">
-        <v>0.825</v>
+        <v>-0.5195</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.9752999999999999</v>
+        <v>-0.9132</v>
       </c>
       <c r="J21" t="n">
-        <v>2.125</v>
+        <v>0.08210000000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>1.9871</v>
+        <v>0.0414</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1378</v>
+        <v>0.0407</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.2753</v>
+        <v>-1.5149</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.1621</v>
+        <v>-0.5609</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.1132</v>
+        <v>-0.9539</v>
       </c>
       <c r="P21" t="n">
-        <v>0.386</v>
+        <v>-0.193</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.9301</v>
+        <v>-0.965</v>
       </c>
       <c r="R21" t="n">
-        <v>2.3161</v>
+        <v>0.772</v>
       </c>
       <c r="S21" t="n">
-        <v>-2.2798</v>
+        <v>-0.5125999999999999</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.1752</v>
+        <v>-0.0231</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.1045</v>
+        <v>-0.4895</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.3281</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0.2859</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.614</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.7763</v>
+        <v>-3.2085</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.311</v>
+        <v>-2.0105</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.4653</v>
+        <v>-1.1979</v>
       </c>
       <c r="G22" t="n">
         <v>-1.9296</v>
@@ -2170,13 +2170,13 @@
         <v>1.3511</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.6188</v>
+        <v>-1.051</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.7297</v>
+        <v>-0.4293</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.889</v>
+        <v>-0.6217</v>
       </c>
       <c r="V22" t="n">
         <v>-0.614</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.8557</v>
+        <v>-5.8035</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.4621</v>
+        <v>-3.0615</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.3936</v>
+        <v>-2.7419</v>
       </c>
       <c r="G23" t="n">
         <v>-3.6006</v>
@@ -2248,13 +2248,13 @@
         <v>1.9301</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.9076</v>
+        <v>-1.8554</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.0271</v>
+        <v>-0.6266</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.8804999999999999</v>
+        <v>-1.2288</v>
       </c>
       <c r="V23" t="n">
         <v>-1.3125</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-7.2029</v>
+        <v>-7.4765</v>
       </c>
       <c r="E24" t="n">
-        <v>-6.5025</v>
+        <v>-6.8029</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.7003</v>
+        <v>-0.6736</v>
       </c>
       <c r="G24" t="n">
         <v>-2.8524</v>
@@ -2326,13 +2326,13 @@
         <v>1.7371</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.6061</v>
+        <v>-0.8798</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.0172</v>
+        <v>-0.3176</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.589</v>
+        <v>-0.5622</v>
       </c>
       <c r="V24" t="n">
         <v>-0.6562</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-21.189</v>
+        <v>-19.8538</v>
       </c>
       <c r="E25" t="n">
-        <v>-12.8188</v>
+        <v>-12.8187</v>
       </c>
       <c r="F25" t="n">
-        <v>-8.370099999999999</v>
+        <v>-7.034800000000001</v>
       </c>
       <c r="G25" t="n">
         <v>-12.0871</v>
@@ -2404,13 +2404,13 @@
         <v>18.3358</v>
       </c>
       <c r="S25" t="n">
-        <v>-13.1405</v>
+        <v>-11.8053</v>
       </c>
       <c r="T25" t="n">
-        <v>-4.0318</v>
+        <v>-4.0317</v>
       </c>
       <c r="U25" t="n">
-        <v>-9.108700000000001</v>
+        <v>-7.7734</v>
       </c>
       <c r="V25" t="n">
         <v>1.1434</v>
